--- a/data/cc.xlsx
+++ b/data/cc.xlsx
@@ -497,7 +497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -509,7 +509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -521,7 +521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>9</v>

--- a/data/cc.xlsx
+++ b/data/cc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Saldo"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>Agencia</t>
   </si>
@@ -35,19 +35,16 @@
     <t>1000,00</t>
   </si>
   <si>
+    <t>'0002</t>
+  </si>
+  <si>
+    <t>20000-2</t>
+  </si>
+  <si>
+    <t>'500,00</t>
+  </si>
+  <si>
     <t>0002</t>
-  </si>
-  <si>
-    <t>20000-2</t>
-  </si>
-  <si>
-    <t>500,00</t>
-  </si>
-  <si>
-    <t>'0002</t>
-  </si>
-  <si>
-    <t>'500,01</t>
   </si>
   <si>
     <t>2000,00</t>
@@ -409,61 +406,56 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -476,61 +468,56 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
